--- a/data/trans_orig/IP07A18-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A18-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2007 (tasa de respuesta: 99,1%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2007 (tasa de respuesta: 99,1%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4999</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7516</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>598</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9352</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11250</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17050</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50408</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59626</t>
+          <t>59327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73667</t>
+          <t>73444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>117005</t>
+          <t>117409</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130912</t>
+          <t>131302</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>643</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>5841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>5417</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2910</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6696</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8381</t>
+          <t>9016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12722</t>
+          <t>12158</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7395</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17394</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>17725</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17054</t>
+          <t>16703</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31551</t>
+          <t>31546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72121</t>
+          <t>71745</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85437</t>
+          <t>85690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70422</t>
+          <t>70120</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83522</t>
+          <t>82734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146977</t>
+          <t>147040</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165427</t>
+          <t>165585</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5855</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>479</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>463</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6600</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1926</t>
+          <t>1701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>15820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29312</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37113</t>
+          <t>36642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>42183</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53088</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81438</t>
+          <t>81887</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98153</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,4%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>8964</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5083</t>
+          <t>4999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>3752</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12979</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7366</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16488</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9903</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22765</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6323</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19852</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>35968</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,11%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>52203</t>
+          <t>52102</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>67683</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>67192</t>
+          <t>67519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80990</t>
+          <t>80747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>123761</t>
+          <t>123937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144538</t>
+          <t>144382</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>76,7%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13818</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7828</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>19818</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14909</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>29809</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8305</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20131</t>
+          <t>20079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>18748</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17852</t>
+          <t>18608</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>11393</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>23644</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>7080</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17779</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20602</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>38001</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>33604</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>53543</t>
+          <t>52873</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31399</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>49887</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70125</t>
+          <t>70336</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>97621</t>
+          <t>96458</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>224753</t>
+          <t>225649</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>250263</t>
+          <t>250763</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>254304</t>
+          <t>256237</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>280096</t>
+          <t>279749</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>490736</t>
+          <t>487335</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>524086</t>
+          <t>523011</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>78,88%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3446</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>10977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15521</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>2694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11921</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7987</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19581</t>
+          <t>18768</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12367</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15939</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24896</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>36290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>49244</t>
+          <t>49554</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38264</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>52248</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79437</t>
+          <t>78886</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98189</t>
+          <t>97752</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,04%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11783</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9222</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21111</t>
+          <t>20272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4418</t>
+          <t>4360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14448</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>28072</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16472</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16814</t>
+          <t>17370</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>4805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13917</t>
+          <t>13839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59733</t>
+          <t>61241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74250</t>
+          <t>75236</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>62,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>55340</t>
+          <t>55938</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>70891</t>
+          <t>70765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120631</t>
+          <t>119966</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141598</t>
+          <t>141728</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,45%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3139</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9643</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>7319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2776</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16633</t>
+          <t>17144</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5944</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15874</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14260</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12490</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3350</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8318</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19820</t>
+          <t>19806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31157</t>
+          <t>30956</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>43377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35218</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48470</t>
+          <t>47851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>70331</t>
+          <t>70250</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87642</t>
+          <t>87630</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,69%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11827</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>7460</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18998</t>
+          <t>19861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6863</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>18778</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4716</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>15171</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14022</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>27790</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11960</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15937</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10449</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19482</t>
+          <t>19755</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6237</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16529</t>
+          <t>16552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>31714</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45408</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>61991</t>
+          <t>62412</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>49253</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65354</t>
+          <t>65686</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>99429</t>
+          <t>99610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122561</t>
+          <t>122308</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31052</t>
+          <t>31270</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33408</t>
+          <t>33433</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>37266</t>
+          <t>38300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60892</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41511</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>21758</t>
+          <t>23042</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39034</t>
+          <t>39199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>50518</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>74079</t>
+          <t>74728</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18798</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>36410</t>
+          <t>35156</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24570</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>42103</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>47465</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>71771</t>
+          <t>71949</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>29172</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>48664</t>
+          <t>47843</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>44694</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>60573</t>
+          <t>62134</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>87318</t>
+          <t>88881</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>188028</t>
+          <t>188446</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>216004</t>
+          <t>216084</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>194452</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>222932</t>
+          <t>222776</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>388322</t>
+          <t>389522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>429204</t>
+          <t>430425</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,9%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de que se riesen de él/ella otros chicos en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de que se riesen de él/ella otros/as chicos/as, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1663</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>9072</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11248</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>17519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2040</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17780</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1255</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>7920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8297,7 +8297,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3490</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12074</t>
+          <t>12513</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3600</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>11883</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8253</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21360</t>
+          <t>20663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43865</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57259</t>
+          <t>56712</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>43063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56680</t>
+          <t>57053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91743</t>
+          <t>92005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110366</t>
+          <t>110689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6031</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23489</t>
+          <t>23614</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13529</t>
+          <t>13048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16101</t>
+          <t>16533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5370</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15052</t>
+          <t>15676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14137</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27785</t>
+          <t>27446</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65898</t>
+          <t>66112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81101</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66563</t>
+          <t>66634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82165</t>
+          <t>81692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>138295</t>
+          <t>137451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159315</t>
+          <t>159632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,25%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>514</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4402</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1429</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4318</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13652</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20048</t>
+          <t>20410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1212</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6907</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2719</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>10620</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8305</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5627</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21205</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51408</t>
+          <t>50751</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>62379</t>
+          <t>62232</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41906</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>56283</t>
+          <t>55571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96431</t>
+          <t>96776</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114840</t>
+          <t>115182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,27%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2224</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2148</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>10441</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16611</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>15594</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6315</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16939</t>
+          <t>16644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18385</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32008</t>
+          <t>31365</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11807</t>
+          <t>11733</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>24262</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43302</t>
+          <t>42987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,57%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>59540</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76867</t>
+          <t>77424</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>55790</t>
+          <t>55807</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>72443</t>
+          <t>72474</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120643</t>
+          <t>120602</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>144100</t>
+          <t>144921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8627</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21052</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14372</t>
+          <t>13792</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29025</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25662</t>
+          <t>25172</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45668</t>
+          <t>44834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>19291</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35410</t>
+          <t>35048</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>16873</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33560</t>
+          <t>33309</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>40274</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>63195</t>
+          <t>63790</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>18676</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>34156</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24871</t>
+          <t>24689</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>42366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>46452</t>
+          <t>48256</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>70706</t>
+          <t>72384</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31016</t>
+          <t>30920</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50507</t>
+          <t>50458</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>32854</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68378</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>95802</t>
+          <t>94505</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>236266</t>
+          <t>235151</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>264931</t>
+          <t>263536</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>222876</t>
+          <t>223033</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>253116</t>
+          <t>252592</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>468261</t>
+          <t>470256</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>509414</t>
+          <t>511187</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
